--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -702,7 +702,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    25/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    26/06/2026</t>
         </is>
       </c>
     </row>
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>43.36</v>
+        <v>43.51</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>41</v>
@@ -954,7 +954,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    25/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    26/06/2026</t>
         </is>
       </c>
     </row>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>175.6</v>
+        <v>175.64</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>12.11</v>
+        <v>12.07</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.69</v>
@@ -1206,7 +1206,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    25/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    26/06/2026</t>
         </is>
       </c>
     </row>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>155.27</v>
+        <v>155.08</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>5.51</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.49</v>
+        <v>3.73</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>115</v>
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>45.53</v>
+        <v>45.36</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2.27</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>43</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>132.42</v>
+        <v>132.14</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6.19</v>
+        <v>6.29</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>100</v>
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>43.51</v>
+        <v>43.35</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1.84</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>41</v>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>175.64</v>
+        <v>175.16</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>12.07</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.69</v>
+        <v>3.95</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>133</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>37.31</v>
+        <v>37.19</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>34</v>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>155.08</v>
+        <v>155.24</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>5.51</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>115</v>
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>45.36</v>
+        <v>45.45</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2.27</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>43</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>132.14</v>
+        <v>132.26</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>100</v>
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>43.35</v>
+        <v>43.43</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1.84</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>41</v>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>175.16</v>
+        <v>175.36</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>12.07</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.95</v>
+        <v>3.69</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>133</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>37.19</v>
+        <v>37.25</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>34</v>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -574,10 +574,10 @@
         <v>3.5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>163.67</v>
+        <v>179.32</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>117</v>
@@ -651,13 +651,13 @@
         <v>8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.88</v>
+        <v>10.8</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="4">
-        <f>G6*1.36</f>
+        <f>G6*1.35</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -702,7 +702,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    26/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    27/06/2026</t>
         </is>
       </c>
     </row>
@@ -826,10 +826,10 @@
         <v>3.11</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>142.32</v>
+        <v>153.71</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>98</v>
@@ -854,19 +854,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>43.43</v>
+        <v>43.41</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1.84</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>49.2</v>
+        <v>50.4</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>37</v>
@@ -903,13 +903,13 @@
         <v>8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.88</v>
+        <v>10.8</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="4">
-        <f>G6*1.36</f>
+        <f>G6*1.35</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -954,7 +954,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    26/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    27/06/2026</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
         <v>3.69</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>189.29</v>
+        <v>203.52</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>127</v>
@@ -1115,10 +1115,10 @@
         <v>2.1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>40.8</v>
+        <v>44.4</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>32</v>
@@ -1155,13 +1155,13 @@
         <v>8</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.88</v>
+        <v>10.8</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="4">
-        <f>G6*1.36</f>
+        <f>G6*1.35</f>
         <v/>
       </c>
       <c r="I6" s="4">
@@ -1206,7 +1206,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    26/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    27/06/2026</t>
         </is>
       </c>
     </row>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -702,7 +702,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    27/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    30/06/2026</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    27/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    30/06/2026</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    27/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    30/06/2026</t>
         </is>
       </c>
     </row>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -702,7 +702,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    30/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    01/07/2026</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    30/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    01/07/2026</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    30/06/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    01/07/2026</t>
         </is>
       </c>
     </row>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -702,7 +702,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    01/07/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    03/07/2026</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    01/07/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    03/07/2026</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    01/07/2026</t>
+          <t>Elaboró: Ing. Mauricio Gastelum Mora    ·    03/07/2026</t>
         </is>
       </c>
     </row>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>155.24</v>
+        <v>155.13</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5.51</v>
+        <v>5.59</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>126</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>132.26</v>
+        <v>132.19</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6.19</v>
+        <v>6.22</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>108</v>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>155.13</v>
+        <v>155.21</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>5.59</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>126</v>
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>45.45</v>
+        <v>45.49</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2.27</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>43</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>132.19</v>
+        <v>132.25</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>6.22</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>108</v>
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>43.41</v>
+        <v>43.45</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1.84</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>42</v>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>175.36</v>
+        <v>175.46</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>12.07</v>
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>37.25</v>
+        <v>37.28</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>1.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>37</v>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>155.21</v>
+        <v>155.32</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5.59</v>
+        <v>5.48</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.51</v>

--- a/Viñas Norte - Generadores.xlsx
+++ b/Viñas Norte - Generadores.xlsx
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>155.32</v>
+        <v>155.21</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5.48</v>
+        <v>5.59</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>3.51</v>
@@ -1069,13 +1069,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>175.46</v>
+        <v>175.54</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>12.07</v>
+        <v>12.75</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>143</v>
